--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طالبات.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الإدارة_طالبات.xlsx
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>رزان علي محمد باعيسى</v>
+        <v>اماني ياسين مسفر الخديدي</v>
       </c>
       <c r="C5" t="str">
         <v>121</v>
@@ -501,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>ابرار محسن جميل الثمالي</v>
+        <v>بيان محمود عبدالله بن ظفران</v>
       </c>
       <c r="C6" t="str">
         <v>227</v>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>امنة حماد محمود الطويرقي</v>
+        <v>اسراء عبدالباقي عبدالرؤوف داود</v>
       </c>
       <c r="C8" t="str">
         <v>224</v>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>رزان علي محمد باعيسى</v>
+        <v>البندري فهد عوضه آل سعييد الشهراني</v>
       </c>
       <c r="C9" t="str">
         <v>121</v>
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>فوزية بخيت مبروك الحارثي</v>
+        <v>مشاعل نافع اسماعيل السهلي</v>
       </c>
       <c r="C13" t="str">
         <v>104</v>
@@ -741,7 +741,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>خلود احمد عيظه آل عصيدان الزهراني</v>
+        <v>غيداء غازي عايض الثبيتي</v>
       </c>
       <c r="C18" t="str">
         <v>225</v>
@@ -761,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="str">
-        <v>خلود احمد عيظه آل عصيدان الزهراني</v>
+        <v>ندى سعد مصلح الحارثي</v>
       </c>
       <c r="C19" t="str">
         <v>225</v>
@@ -781,7 +781,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="str">
-        <v>ابرار محسن جميل الثمالي</v>
+        <v>هناء محمد سعيد سويد</v>
       </c>
       <c r="C20" t="str">
         <v>227</v>
@@ -821,7 +821,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="str">
-        <v>رقية بدوي أحمد آل أحمد الزبيدي</v>
+        <v>حنان عثمان عمسيب محمد</v>
       </c>
       <c r="C22" t="str">
         <v>223</v>
@@ -841,7 +841,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="str">
-        <v>امنة حماد محمود الطويرقي</v>
+        <v>شيرين شريف عبداللطيف شريف</v>
       </c>
       <c r="C23" t="str">
         <v>224</v>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="str">
-        <v>رقية بدوي أحمد آل أحمد الزبيدي</v>
+        <v>منى النيل مصطفي مرسال</v>
       </c>
       <c r="C24" t="str">
         <v>223</v>
